--- a/templates/engagements-template.xlsx
+++ b/templates/engagements-template.xlsx
@@ -679,7 +679,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -693,8 +693,9 @@
     <col width="21" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
-    <col width="34" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="34" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -755,10 +756,15 @@
       </c>
       <c r="L1" s="3" t="inlineStr">
         <is>
+          <t>Invoice code</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="M1" s="3" t="inlineStr">
+      <c r="N1" s="3" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
@@ -820,10 +826,15 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
           <t>Example row - replace with a real client</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -834,7 +845,7 @@
     <dataValidation sqref="G2:G400" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"email,portal"</formula1>
     </dataValidation>
-    <dataValidation sqref="M2:M400" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="N2:N400" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"yes,no"</formula1>
     </dataValidation>
   </dataValidations>
@@ -848,17 +859,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="19" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="19" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -869,35 +881,40 @@
       </c>
       <c r="B1" s="3" t="inlineStr">
         <is>
+          <t>Initials</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
           <t>Other names</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Vendor company</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>Paid by</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="H1" s="3" t="inlineStr">
         <is>
           <t>Pay timing (days)</t>
         </is>
       </c>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="I1" s="3" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
@@ -909,31 +926,32 @@
           <t>Priya Shah</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
         <is>
           <t>P. Shah; Shah, Priya</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>priya@example.com</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>contractor</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr">
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
         <is>
           <t>bank transfer</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>15</v>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -941,13 +959,13 @@
     </row>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation sqref="D2:D400" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E2:E400" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"employee,contractor,vendor"</formula1>
     </dataValidation>
-    <dataValidation sqref="F2:F400" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G2:G400" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"bank transfer,payroll,check,other"</formula1>
     </dataValidation>
-    <dataValidation sqref="H2:H400" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I2:I400" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"yes,no"</formula1>
     </dataValidation>
   </dataValidations>

--- a/templates/engagements-template.xlsx
+++ b/templates/engagements-template.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -564,12 +564,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Changing a rate</t>
+          <t>Salaried employees</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Add a new Engagements row with the new rates and the date they</t>
+          <t>An Icon employee on a fixed salary: Type 'employee', Paid by</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       <c r="A17" s="2" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>start in 'Rates from'. Leave the old row alone: it is the record of</t>
+          <t>'salary', Pay timing blank, and Pay rate blank on their Engagements</t>
         </is>
       </c>
     </row>
@@ -585,45 +585,46 @@
       <c r="A18" s="2" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>what was charged before.</t>
+          <t>rows. The client is still billed at the Bill rate; you get a reminder</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>to pay the month's salary instead of an amount owed.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>Dates</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Type them as 2026-02-01. Excel may show them differently once you</t>
-        </is>
-      </c>
+      <c r="A20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr"/>
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Changing a rate</t>
+        </is>
+      </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>press Enter; that is fine, the agent reads the underlying date.</t>
+          <t>Add a new Engagements row with the new rates and the date they</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>start in 'Rates from'. Leave the old row alone: it is the record of</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>Money</t>
-        </is>
-      </c>
+      <c r="A23" s="2" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Dollars with cents, like 140.00. No currency symbol needed.</t>
+          <t>what was charged before.</t>
         </is>
       </c>
     </row>
@@ -633,40 +634,78 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Yes / no columns</t>
+          <t>Dates</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Pick from the dropdown. Blank is not the same as 'no'.</t>
+          <t>Type them as 2026-02-01. Excel may show them differently once you</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>press Enter; that is fine, the agent reads the underlying date.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="A27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Money</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Dollars with cents, like 140.00. No currency symbol needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Yes / no columns</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Pick from the dropdown. Blank is not the same as 'no'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>If something is wrong</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>The agent never guesses and never edits this file. It emails</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr"/>
-      <c r="B28" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
         <is>
           <t>Kevin naming the sheet and the row number, and waits.</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="n"/>
+    <row r="34">
+      <c r="A34" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -963,7 +1002,7 @@
       <formula1>"employee,contractor,vendor"</formula1>
     </dataValidation>
     <dataValidation sqref="G2:G400" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"bank transfer,payroll,check,other"</formula1>
+      <formula1>"bank transfer,payroll,check,other,salary"</formula1>
     </dataValidation>
     <dataValidation sqref="I2:I400" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"yes,no"</formula1>
